--- a/FlyingWingParams.xlsx
+++ b/FlyingWingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U511\MATLAB\Projects\AAE451\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FB330A2-DF8C-4EF3-8D0B-29E743CFDD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92787BA3-43D6-45EC-B1D2-8CF3412A0F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="21490" windowWidth="38620" windowHeight="11220" xr2:uid="{3E3C860D-C0B8-46AE-8B79-8473AEA7E990}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E3C860D-C0B8-46AE-8B79-8473AEA7E990}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Aircraft</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Service Ceiling (km)</t>
   </si>
   <si>
-    <t>Boeing X-45</t>
-  </si>
-  <si>
     <t>NG X-47A Pegasus</t>
   </si>
   <si>
@@ -93,6 +90,27 @@
   </si>
   <si>
     <t>Northrop B-2 Spirit</t>
+  </si>
+  <si>
+    <t>Northrop YB-49</t>
+  </si>
+  <si>
+    <t>Northrop XP-79B</t>
+  </si>
+  <si>
+    <t>Horten Ho 229</t>
+  </si>
+  <si>
+    <t>Horten Ho 229A</t>
+  </si>
+  <si>
+    <t>Boeing X-48B</t>
+  </si>
+  <si>
+    <t>Boeing X-45A</t>
+  </si>
+  <si>
+    <t>Martin Marietta X-24</t>
   </si>
 </sst>
 </file>
@@ -465,21 +483,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2FB1E2-0D4E-4FD2-969E-783EBC98247D}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.68359375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.20703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.47265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.3671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.47265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.20703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -537,7 +555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -566,7 +584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -595,7 +613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -624,9 +642,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>3629</v>
@@ -653,9 +671,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>1740</v>
@@ -682,9 +700,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>13080</v>
@@ -711,9 +729,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>17690</v>
@@ -740,9 +758,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>2050</v>
@@ -769,9 +787,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>71700</v>
@@ -796,6 +814,180 @@
       </c>
       <c r="I11">
         <v>15.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>40117</v>
+      </c>
+      <c r="C12">
+        <v>87969</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>144</v>
+      </c>
+      <c r="F12">
+        <v>16.18</v>
+      </c>
+      <c r="G12">
+        <v>52.43</v>
+      </c>
+      <c r="H12">
+        <v>0.74</v>
+      </c>
+      <c r="I12">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>2650</v>
+      </c>
+      <c r="C13">
+        <v>3932</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F13">
+        <v>4.26</v>
+      </c>
+      <c r="G13">
+        <v>11.58</v>
+      </c>
+      <c r="H13">
+        <v>0.83</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>4844</v>
+      </c>
+      <c r="C14">
+        <v>6876</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>17.66</v>
+      </c>
+      <c r="F14">
+        <v>7.4</v>
+      </c>
+      <c r="G14">
+        <v>16.8</v>
+      </c>
+      <c r="H14">
+        <v>0.92</v>
+      </c>
+      <c r="I14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>4600</v>
+      </c>
+      <c r="C15">
+        <v>8100</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>17.66</v>
+      </c>
+      <c r="F15">
+        <v>7.47</v>
+      </c>
+      <c r="G15">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="H15">
+        <v>0.92</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>178</v>
+      </c>
+      <c r="C16">
+        <v>227</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>0.69</v>
+      </c>
+      <c r="F16">
+        <v>10.7</v>
+      </c>
+      <c r="G16">
+        <v>6.4</v>
+      </c>
+      <c r="H16">
+        <v>0.18</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>3538</v>
+      </c>
+      <c r="C17">
+        <v>6260</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>36</v>
+      </c>
+      <c r="F17">
+        <v>11.43</v>
+      </c>
+      <c r="G17">
+        <v>5.84</v>
+      </c>
+      <c r="H17">
+        <v>1.52</v>
+      </c>
+      <c r="I17">
+        <v>22.59</v>
       </c>
     </row>
   </sheetData>
